--- a/clients/encore/testcases/corporate-override/corporate-override-nm2271.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-nm2271.xlsx
@@ -52,7 +52,7 @@
     <t>Notes / Reason</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-050</t>
+    <t>TC-CPR-OVR-049</t>
   </si>
   <si>
     <t>Labor tab renders a populated grid with real data on office 9460</t>
@@ -113,7 +113,7 @@
     <t>The Labor tab renders a populated grid with real data: rows are visible, the items-found total is in the triple digits, and the known anchor row is present</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-051</t>
+    <t>TC-CPR-OVR-050</t>
   </si>
   <si>
     <t>Labor grid text filter narrows to matching rows and clearing restores the page</t>
@@ -153,7 +153,7 @@
     <t>The visible row count increases back above the narrowed count.</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-052</t>
+    <t>TC-CPR-OVR-051</t>
   </si>
   <si>
     <t>Labor grid column sort orders Product Group Name ascending and descending</t>
@@ -177,7 +177,7 @@
     <t>The Labor grid sorts via the same header dropdown mechanism as Equipment. The oracle is self-verifying monotonic order - resilient to data drift on the shared bed</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-053</t>
+    <t>TC-CPR-OVR-052</t>
   </si>
   <si>
     <t>Labor Override Price save-cycle persists after reload and restores</t>
@@ -215,43 +215,43 @@
     <t>Override Price for row 655 displays 161.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-053</t>
+  </si>
+  <si>
+    <t>Labor Max Discount % save-cycle persists after reload and restores</t>
+  </si>
+  <si>
+    <t>Office 1105 Labor row 655 at baseline (Max Discount unset "-")</t>
+  </si>
+  <si>
+    <t>1. Baseline restore</t>
+  </si>
+  <si>
+    <t>Max Discount % for row 655 accepts the value 10 and the Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>2. Save + confirm</t>
+  </si>
+  <si>
+    <t>Max Discount % for row 655 displays 10 after reload.</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-054</t>
   </si>
   <si>
-    <t>Labor Max Discount % save-cycle persists after reload and restores</t>
-  </si>
-  <si>
-    <t>Office 1105 Labor row 655 at baseline (Max Discount unset "-")</t>
-  </si>
-  <si>
-    <t>1. Baseline restore</t>
-  </si>
-  <si>
-    <t>Max Discount % for row 655 accepts the value 10 and the Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>2. Save + confirm</t>
-  </si>
-  <si>
-    <t>Max Discount % for row 655 displays 10 after reload.</t>
+    <t>Labor Active toggle save-cycle persists after reload and restores</t>
+  </si>
+  <si>
+    <t>Office 1105 Labor row 655 at baseline (inactive)</t>
+  </si>
+  <si>
+    <t>The Active checkbox toggles to the opposite state and the Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>The toggled Active state is displayed after reload.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-055</t>
-  </si>
-  <si>
-    <t>Labor Active toggle save-cycle persists after reload and restores</t>
-  </si>
-  <si>
-    <t>Office 1105 Labor row 655 at baseline (inactive)</t>
-  </si>
-  <si>
-    <t>The Active checkbox toggles to the opposite state and the Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>The toggled Active state is displayed after reload.</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-056</t>
   </si>
   <si>
     <t>Navigating away from a dirty grid raises the unsaved-changes dialog; Stay keeps the page and the edit</t>
@@ -302,31 +302,31 @@
     <t>The Save button remains enabled.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-056</t>
+  </si>
+  <si>
+    <t>Discard in the unsaved-changes dialog leaves the page and drops the edit</t>
+  </si>
+  <si>
+    <t>1. Edit row 655 Override Price</t>
+  </si>
+  <si>
+    <t>An unsaved-changes dialog opens with a Discard option.</t>
+  </si>
+  <si>
+    <t>3. Assert navigation to the home page</t>
+  </si>
+  <si>
+    <t>The application navigates to the home page.</t>
+  </si>
+  <si>
+    <t>4. Re-open the Override screen + re-select 1105 + Labor tab</t>
+  </si>
+  <si>
+    <t>Discard navigates away and the dropped edit never persists - proven by re-reading the value after a full reload</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-057</t>
-  </si>
-  <si>
-    <t>Discard in the unsaved-changes dialog leaves the page and drops the edit</t>
-  </si>
-  <si>
-    <t>1. Edit row 655 Override Price</t>
-  </si>
-  <si>
-    <t>An unsaved-changes dialog opens with a Discard option.</t>
-  </si>
-  <si>
-    <t>3. Assert navigation to the home page</t>
-  </si>
-  <si>
-    <t>The application navigates to the home page.</t>
-  </si>
-  <si>
-    <t>4. Re-open the Override screen + re-select 1105 + Labor tab</t>
-  </si>
-  <si>
-    <t>Discard navigates away and the dropped edit never persists - proven by re-reading the value after a full reload</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-058</t>
   </si>
   <si>
     <t>Page navigation changes the visible rows and enables or disables the nav buttons at each end</t>
@@ -374,7 +374,7 @@
     <t>The visible row count is between 1 and the current rows-per-page setting.</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-059</t>
+    <t>TC-CPR-OVR-058</t>
   </si>
   <si>
     <t>Raising rows-per-page shows more rows without changing the total</t>
@@ -407,7 +407,7 @@
     <t>A larger page size shows more rows on the page while the underlying record total stays constant. Relative assertions only</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-060</t>
+    <t>TC-CPR-OVR-059</t>
   </si>
   <si>
     <t>A page-1 row reads back identically after paging to the last page and returning</t>
@@ -431,40 +431,40 @@
     <t>content-based read integrity holds across a full page-range round trip on the largest available data set - no windowing or render corruption. content, never position</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-061</t>
+  </si>
+  <si>
+    <t>Enter opens the Override Price editor on a focused cell; Escape closes it without dirtying the form</t>
+  </si>
+  <si>
+    <t>Office 1606 fixture row at its default; grid clean</t>
+  </si>
+  <si>
+    <t>1. Focus the anchor row Override Price display cell (it is keyboard-focusable)</t>
+  </si>
+  <si>
+    <t>The Override Price display cell receives keyboard focus.</t>
+  </si>
+  <si>
+    <t>2. Press Enter</t>
+  </si>
+  <si>
+    <t>The numeric editor opens and displays the current Override Price value.</t>
+  </si>
+  <si>
+    <t>3. Press Escape</t>
+  </si>
+  <si>
+    <t>The editor closes without committing a change.</t>
+  </si>
+  <si>
+    <t>4. Save remains disabled (no unsaved changes)</t>
+  </si>
+  <si>
+    <t>The Save button remains disabled.</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-062</t>
-  </si>
-  <si>
-    <t>Enter opens the Override Price editor on a focused cell; Escape closes it without dirtying the form</t>
-  </si>
-  <si>
-    <t>Office 1606 fixture row at its default; grid clean</t>
-  </si>
-  <si>
-    <t>1. Focus the anchor row Override Price display cell (it is keyboard-focusable)</t>
-  </si>
-  <si>
-    <t>The Override Price display cell receives keyboard focus.</t>
-  </si>
-  <si>
-    <t>2. Press Enter</t>
-  </si>
-  <si>
-    <t>The numeric editor opens and displays the current Override Price value.</t>
-  </si>
-  <si>
-    <t>3. Press Escape</t>
-  </si>
-  <si>
-    <t>The editor closes without committing a change.</t>
-  </si>
-  <si>
-    <t>4. Save remains disabled (no unsaved changes)</t>
-  </si>
-  <si>
-    <t>The Save button remains disabled.</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-063</t>
   </si>
   <si>
     <t>The Product Group picker appears only when a specific currency is selected</t>
@@ -497,66 +497,66 @@
     <t>The add-override affordance is a currency-gated picker: absent on ALL, present with draggable rows once a specific currency is selected</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-063</t>
+  </si>
+  <si>
+    <t>Dragging a picker row stages a new override row with no request until Save; Discard drops it</t>
+  </si>
+  <si>
+    <t>Office 4104 selected; Currency USD; picker visible; Equipment tab</t>
+  </si>
+  <si>
+    <t>1. Read the grid row count</t>
+  </si>
+  <si>
+    <t>The current grid row count is displayed.</t>
+  </si>
+  <si>
+    <t>2. Drag the picker first row into the Equipment grid panel</t>
+  </si>
+  <si>
+    <t>The dragged row is added to the Equipment grid.</t>
+  </si>
+  <si>
+    <t>3. Assert: row count +1</t>
+  </si>
+  <si>
+    <t>The grid row count increases by 1.</t>
+  </si>
+  <si>
+    <t>4. ZERO save requests fired during the drag</t>
+  </si>
+  <si>
+    <t>No save request fires during the drag.</t>
+  </si>
+  <si>
+    <t>5. Save button enabled</t>
+  </si>
+  <si>
+    <t>The Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>6. the staged row shows Override Price 0.00 and inactive</t>
+  </si>
+  <si>
+    <t>The staged row displays Override Price 0.00 and the Active checkbox unchecked.</t>
+  </si>
+  <si>
+    <t>7. Navigate Home</t>
+  </si>
+  <si>
+    <t>An unsaved-changes dialog opens, and Discard navigates to the home page.</t>
+  </si>
+  <si>
+    <t>8. Re-open + re-select 4104 + USD</t>
+  </si>
+  <si>
+    <t>Drag staging is purely client-side (no request until Save), lands at 0.00/inactive, dirties the form, and evaporates on Discard - proven by a post-reload recount. Nothing is ever saved</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-064</t>
   </si>
   <si>
-    <t>Dragging a picker row stages a new override row with no request until Save; Discard drops it</t>
-  </si>
-  <si>
-    <t>Office 4104 selected; Currency USD; picker visible; Equipment tab</t>
-  </si>
-  <si>
-    <t>1. Read the grid row count</t>
-  </si>
-  <si>
-    <t>The current grid row count is displayed.</t>
-  </si>
-  <si>
-    <t>2. Drag the picker first row into the Equipment grid panel</t>
-  </si>
-  <si>
-    <t>The dragged row is added to the Equipment grid.</t>
-  </si>
-  <si>
-    <t>3. Assert: row count +1</t>
-  </si>
-  <si>
-    <t>The grid row count increases by 1.</t>
-  </si>
-  <si>
-    <t>4. ZERO save requests fired during the drag</t>
-  </si>
-  <si>
-    <t>No save request fires during the drag.</t>
-  </si>
-  <si>
-    <t>5. Save button enabled</t>
-  </si>
-  <si>
-    <t>The Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>6. the staged row shows Override Price 0.00 and inactive</t>
-  </si>
-  <si>
-    <t>The staged row displays Override Price 0.00 and the Active checkbox unchecked.</t>
-  </si>
-  <si>
-    <t>7. Navigate Home</t>
-  </si>
-  <si>
-    <t>An unsaved-changes dialog opens, and Discard navigates to the home page.</t>
-  </si>
-  <si>
-    <t>8. Re-open + re-select 4104 + USD</t>
-  </si>
-  <si>
-    <t>Drag staging is purely client-side (no request until Save), lands at 0.00/inactive, dirties the form, and evaporates on Discard - proven by a post-reload recount. Nothing is ever saved</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-065</t>
-  </si>
-  <si>
     <t>The picker serves the Labor tab and drag staging works there too</t>
   </si>
   <si>
@@ -587,136 +587,136 @@
     <t>The same currency-gated picker serves Labor product groups, and drag staging behaves identically on the Labor tab</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-083</t>
+  </si>
+  <si>
+    <t>Clicking Override Price cell on Labor reveals an editable field</t>
+  </si>
+  <si>
+    <t>Authenticated; on the Override screen with office 1134 selected, Labor tab active</t>
+  </si>
+  <si>
+    <t>1. Navigate to Labor tab on office 1134, find row by Product Group 565</t>
+  </si>
+  <si>
+    <t>Office 1134 loads on the Labor tab with the Product Group 565 row visible.</t>
+  </si>
+  <si>
+    <t>2. Click the Override Price cell (role=button)</t>
+  </si>
+  <si>
+    <t>The Override Price cell switches to edit mode.</t>
+  </si>
+  <si>
+    <t>3. Read the editor value</t>
+  </si>
+  <si>
+    <t>The editor displays the pre-filled value 13.00.</t>
+  </si>
+  <si>
+    <t>4. Press Escape</t>
+  </si>
+  <si>
+    <t>The Override Price cell on Labor is click-to-edit - clicking reveals a field pre-filled with the current value (13.00 for PG 565)</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-084</t>
   </si>
   <si>
-    <t>Clicking Override Price cell on Labor reveals an editable field</t>
-  </si>
-  <si>
-    <t>Authenticated; on the Override screen with office 1134 selected, Labor tab active</t>
-  </si>
-  <si>
-    <t>1. Navigate to Labor tab on office 1134, find row by Product Group 565</t>
-  </si>
-  <si>
-    <t>Office 1134 loads on the Labor tab with the Product Group 565 row visible.</t>
-  </si>
-  <si>
-    <t>2. Click the Override Price cell (role=button)</t>
-  </si>
-  <si>
-    <t>The Override Price cell switches to edit mode.</t>
-  </si>
-  <si>
-    <t>3. Read the editor value</t>
-  </si>
-  <si>
-    <t>The editor displays the pre-filled value 13.00.</t>
-  </si>
-  <si>
-    <t>4. Press Escape</t>
-  </si>
-  <si>
-    <t>The Override Price cell on Labor is click-to-edit - clicking reveals a field pre-filled with the current value (13.00 for PG 565)</t>
+    <t>Override Price accepts 0 on Labor (min valid)</t>
+  </si>
+  <si>
+    <t>On the Override screen, office 1134, Labor tab, PG 565 row visible</t>
+  </si>
+  <si>
+    <t>1. Navigate to Labor row PG 565 (reload restores originals)</t>
+  </si>
+  <si>
+    <t>The Labor row for PG 565 is displayed with its original Override Price.</t>
+  </si>
+  <si>
+    <t>2. Call</t>
+  </si>
+  <si>
+    <t>The value 0 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='0.00', saveEnabled=true</t>
+  </si>
+  <si>
+    <t>Override Price accepts 0 as a valid value; editor closes; cell displays 0.00; Save enables</t>
   </si>
   <si>
     <t>TC-CPR-OVR-085</t>
   </si>
   <si>
-    <t>Override Price accepts 0 on Labor (min valid)</t>
-  </si>
-  <si>
-    <t>On the Override screen, office 1134, Labor tab, PG 565 row visible</t>
-  </si>
-  <si>
-    <t>1. Navigate to Labor row PG 565 (reload restores originals)</t>
-  </si>
-  <si>
-    <t>The Labor row for PG 565 is displayed with its original Override Price.</t>
-  </si>
-  <si>
-    <t>2. Call</t>
-  </si>
-  <si>
-    <t>The value 0 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='0.00', saveEnabled=true</t>
-  </si>
-  <si>
-    <t>Override Price accepts 0 as a valid value; editor closes; cell displays 0.00; Save enables</t>
+    <t>Override Price accepts mid-value decimal on Labor (25.50)</t>
+  </si>
+  <si>
+    <t>The value 25.50 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='25.50', saveEnabled=true</t>
+  </si>
+  <si>
+    <t>Override Price accepts a mid-range decimal; editor closes; cell displays 25.50; Save enables</t>
   </si>
   <si>
     <t>TC-CPR-OVR-086</t>
   </si>
   <si>
-    <t>Override Price accepts mid-value decimal on Labor (25.50)</t>
-  </si>
-  <si>
-    <t>The value 25.50 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='25.50', saveEnabled=true</t>
-  </si>
-  <si>
-    <t>Override Price accepts a mid-range decimal; editor closes; cell displays 25.50; Save enables</t>
+    <t>Override Price accepts a large value on Labor (9999.99)</t>
+  </si>
+  <si>
+    <t>The value 9999.99 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='9,999.99', saveEnabled=true</t>
+  </si>
+  <si>
+    <t>Override Price accepts a large value; editor closes; cell renders with thousands separator as 9,999.99; Save enables</t>
   </si>
   <si>
     <t>TC-CPR-OVR-087</t>
   </si>
   <si>
-    <t>Override Price accepts a large value on Labor (9999.99)</t>
-  </si>
-  <si>
-    <t>The value 9999.99 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='9,999.99', saveEnabled=true</t>
-  </si>
-  <si>
-    <t>Override Price accepts a large value; editor closes; cell renders with thousands separator as 9,999.99; Save enables</t>
+    <t>Override Price rejects -0.01 on Labor (below-min boundary)</t>
+  </si>
+  <si>
+    <t>The value -0.01 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert: committed=false, ariaInvalid='true', borderColor contains oklch(0.577 0.245 27.325), errorText='' (no message - defect #4), saveEnabled=false, escapable=true</t>
+  </si>
+  <si>
+    <t>-0.01 is rejected - editor stays open, is invalid, red border, Save disabled, no error message (defect #4), escapable via Tab</t>
   </si>
   <si>
     <t>TC-CPR-OVR-088</t>
   </si>
   <si>
-    <t>Override Price rejects -0.01 on Labor (below-min boundary)</t>
-  </si>
-  <si>
-    <t>The value -0.01 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert: committed=false, ariaInvalid='true', borderColor contains oklch(0.577 0.245 27.325), errorText='' (no message - defect #4), saveEnabled=false, escapable=true</t>
-  </si>
-  <si>
-    <t>-0.01 is rejected - editor stays open, is invalid, red border, Save disabled, no error message (defect #4), escapable via Tab</t>
+    <t>Override Price accepts 0.01 on Labor (just above zero)</t>
+  </si>
+  <si>
+    <t>On the Override screen, office 1134, Labor tab, PG 893 row visible</t>
+  </si>
+  <si>
+    <t>1. Navigate to Labor row PG 893 (reload restores originals)</t>
+  </si>
+  <si>
+    <t>The Labor row for PG 893 is displayed with its original Override Price.</t>
+  </si>
+  <si>
+    <t>The value 0.01 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='0.01', saveEnabled=true</t>
+  </si>
+  <si>
+    <t>The smallest positive decimal step commits - cell displays 0.01, Save enables</t>
   </si>
   <si>
     <t>TC-CPR-OVR-089</t>
-  </si>
-  <si>
-    <t>Override Price accepts 0.01 on Labor (just above zero)</t>
-  </si>
-  <si>
-    <t>On the Override screen, office 1134, Labor tab, PG 893 row visible</t>
-  </si>
-  <si>
-    <t>1. Navigate to Labor row PG 893 (reload restores originals)</t>
-  </si>
-  <si>
-    <t>The Labor row for PG 893 is displayed with its original Override Price.</t>
-  </si>
-  <si>
-    <t>The value 0.01 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='0.01', saveEnabled=true</t>
-  </si>
-  <si>
-    <t>The smallest positive decimal step commits - cell displays 0.01, Save enables</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-090</t>
   </si>
   <si>
     <t>Override Price 3rd decimal precision on Labor (12.345)</t>
@@ -743,28 +743,28 @@
     <t>A 3rd-decimal-place input commits (editor closes, Save enables). Exact displayed format is "Pending verification" - precision/rounding behavior on Override Price has not been probed</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-090</t>
+  </si>
+  <si>
+    <t>Override Price above-max probe on Labor (999999.99)</t>
+  </si>
+  <si>
+    <t>The value 999999.99 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='999,999.99', saveEnabled=true - "Pending verification": no confirmed hard max for Override Price</t>
+  </si>
+  <si>
+    <t>The value commits and displays as 999,999.99, and the Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>4. if rejected, apply override rejection signature instead</t>
+  </si>
+  <si>
+    <t>"Pending verification" - no confirmed hard max for Override Price exists. If accepted: displays 999,999.99. If rejected: full rejection signature applies. TC-021 on Equipment states "a large number" is accepted, so acceptance is the expected path</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-091</t>
-  </si>
-  <si>
-    <t>Override Price above-max probe on Labor (999999.99)</t>
-  </si>
-  <si>
-    <t>The value 999999.99 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='999,999.99', saveEnabled=true - "Pending verification": no confirmed hard max for Override Price</t>
-  </si>
-  <si>
-    <t>The value commits and displays as 999,999.99, and the Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>4. if rejected, apply override rejection signature instead</t>
-  </si>
-  <si>
-    <t>"Pending verification" - no confirmed hard max for Override Price exists. If accepted: displays 999,999.99. If rejected: full rejection signature applies. TC-021 on Equipment states "a large number" is accepted, so acceptance is the expected path</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-092</t>
   </si>
   <si>
     <t>Defect - abc blanks Override Price to dash, Save stays enabled (Labor)</t>
@@ -791,250 +791,250 @@
     <t>The defect is documented: non-numeric input blanks the Override Price cell instead of being rejected.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-092</t>
+  </si>
+  <si>
+    <t>Defect - 1.2.3 silently corrupts Override Price to 1.23 (Labor)</t>
+  </si>
+  <si>
+    <t>2. Call - real keyboard input (method rule)</t>
+  </si>
+  <si>
+    <t>The characters 1.2.3 are typed into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert the DEFECT: committed=true, displayedValue='1.23' (no % suffix - Override Price format), saveEnabled=true</t>
+  </si>
+  <si>
+    <t>The value commits as 1.23, the editor closes, and the Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>4. "Expected (asserting the BUG - test FAILS when app is fixed)": 1.2.3 (a typo) is not rejected - the browser swallows the second dot, committing 1.23 as if valid. When fixed, the app will reject 1.2.3 and committed will become false</t>
+  </si>
+  <si>
+    <t>The defect is documented: the app accepts 1.2.3 as 1.23 instead of rejecting the malformed multi-dot input.</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-093</t>
   </si>
   <si>
-    <t>Defect - 1.2.3 silently corrupts Override Price to 1.23 (Labor)</t>
-  </si>
-  <si>
-    <t>2. Call - real keyboard input (method rule)</t>
-  </si>
-  <si>
-    <t>The characters 1.2.3 are typed into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert the DEFECT: committed=true, displayedValue='1.23' (no % suffix - Override Price format), saveEnabled=true</t>
-  </si>
-  <si>
-    <t>The value commits as 1.23, the editor closes, and the Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>4. "Expected (asserting the BUG - test FAILS when app is fixed)": 1.2.3 (a typo) is not rejected - the browser swallows the second dot, committing 1.23 as if valid. When fixed, the app will reject 1.2.3 and committed will become false</t>
-  </si>
-  <si>
-    <t>The defect is documented: the app accepts 1.2.3 as 1.23 instead of rejecting the malformed multi-dot input.</t>
+    <t>Rejected - negative -5 on Override Price with full affordance oracle (Labor)</t>
+  </si>
+  <si>
+    <t>2. Call - captures step-5 order BEFORE escape</t>
+  </si>
+  <si>
+    <t>The value -5 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert rejection oracle (all 7 affordances):</t>
+  </si>
+  <si>
+    <t>The editor remains open with the rejected value -5 still displayed.</t>
+  </si>
+  <si>
+    <t>4. - committed = false (editor stays open, value NOT committed)</t>
+  </si>
+  <si>
+    <t>The value is not committed and the Override Price editor stays open.</t>
+  </si>
+  <si>
+    <t>5. - ariaInvalid = 'true'</t>
+  </si>
+  <si>
+    <t>The field is displayed marked as invalid.</t>
+  </si>
+  <si>
+    <t>6. - borderColor contains oklch(0.577 0.245 27.325) (red)</t>
+  </si>
+  <si>
+    <t>The field border is displayed in red.</t>
+  </si>
+  <si>
+    <t>7. - errorText = '' (empty - defect #4: no error message ever shown)</t>
+  </si>
+  <si>
+    <t>No error message text is displayed next to the field.</t>
+  </si>
+  <si>
+    <t>8. - saveEnabled = false (Save DISABLED)</t>
+  </si>
+  <si>
+    <t>The Save button is displayed disabled.</t>
+  </si>
+  <si>
+    <t>9. - escapable = true (Tab moves focus out - NOT a focus trap)</t>
+  </si>
+  <si>
+    <t>Pressing Tab moves focus out of the field.</t>
+  </si>
+  <si>
+    <t>10. Assert [ ] displayed text is empty (defect #4 evidence)</t>
+  </si>
+  <si>
+    <t>-5 is rejected with the full override rejection signature. The rejection is LOUD (visual cues) but SILENT (no error text - defect #4). Editor stays open; Save is disabled; focus is NOT trapped</t>
   </si>
   <si>
     <t>TC-CPR-OVR-094</t>
   </si>
   <si>
-    <t>Rejected - negative -5 on Override Price with full affordance oracle (Labor)</t>
-  </si>
-  <si>
-    <t>2. Call - captures step-5 order BEFORE escape</t>
-  </si>
-  <si>
-    <t>The value -5 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert rejection oracle (all 7 affordances):</t>
-  </si>
-  <si>
-    <t>The editor remains open with the rejected value -5 still displayed.</t>
-  </si>
-  <si>
-    <t>4. - committed = false (editor stays open, value NOT committed)</t>
-  </si>
-  <si>
-    <t>The value is not committed and the Override Price editor stays open.</t>
-  </si>
-  <si>
-    <t>5. - ariaInvalid = 'true'</t>
-  </si>
-  <si>
-    <t>The field is displayed marked as invalid.</t>
-  </si>
-  <si>
-    <t>6. - borderColor contains oklch(0.577 0.245 27.325) (red)</t>
-  </si>
-  <si>
-    <t>The field border is displayed in red.</t>
-  </si>
-  <si>
-    <t>7. - errorText = '' (empty - defect #4: no error message ever shown)</t>
-  </si>
-  <si>
-    <t>No error message text is displayed next to the field.</t>
-  </si>
-  <si>
-    <t>8. - saveEnabled = false (Save DISABLED)</t>
-  </si>
-  <si>
-    <t>The Save button is displayed disabled.</t>
-  </si>
-  <si>
-    <t>9. - escapable = true (Tab moves focus out - NOT a focus trap)</t>
-  </si>
-  <si>
-    <t>Pressing Tab moves focus out of the field.</t>
-  </si>
-  <si>
-    <t>10. Assert [ ] displayed text is empty (defect #4 evidence)</t>
-  </si>
-  <si>
-    <t>-5 is rejected with the full override rejection signature. The rejection is LOUD (visual cues) but SILENT (no error text - defect #4). Editor stays open; Save is disabled; focus is NOT trapped</t>
+    <t>Override Price leading zeros stripped on Labor (007 -&gt; 7.00)</t>
+  </si>
+  <si>
+    <t>The value 007 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='7.00', saveEnabled=true</t>
+  </si>
+  <si>
+    <t>Leading zeros are stripped - 007 commits as 7.00 (no % suffix on Override Price). Save enables</t>
   </si>
   <si>
     <t>TC-CPR-OVR-095</t>
   </si>
   <si>
-    <t>Override Price leading zeros stripped on Labor (007 -&gt; 7.00)</t>
-  </si>
-  <si>
-    <t>The value 007 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='7.00', saveEnabled=true</t>
-  </si>
-  <si>
-    <t>Leading zeros are stripped - 007 commits as 7.00 (no % suffix on Override Price). Save enables</t>
+    <t>Override Price scientific notation 1e5 on Labor</t>
+  </si>
+  <si>
+    <t>The value 1e5 is entered into the Override Price field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>3. Assert committed=true, displayedValue='100,000.00', saveEnabled=true</t>
+  </si>
+  <si>
+    <t>1e5 commits on Override Price and displays as 100,000.00. Save enables. Max Discount % rejects 1e5 because the &gt;100 cap fires (1e5 = 100000 &gt; 100), not because the app refuses scientific notation; Override Price has no such cap, so it accepts the value</t>
   </si>
   <si>
     <t>TC-CPR-OVR-096</t>
   </si>
   <si>
-    <t>Override Price scientific notation 1e5 on Labor</t>
-  </si>
-  <si>
-    <t>The value 1e5 is entered into the Override Price field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>3. Assert committed=true, displayedValue='100,000.00', saveEnabled=true</t>
-  </si>
-  <si>
-    <t>1e5 commits on Override Price and displays as 100,000.00. Save enables. Max Discount % rejects 1e5 because the &gt;100 cap fires (1e5 = 100000 &gt; 100), not because the app refuses scientific notation; Override Price has no such cap, so it accepts the value</t>
+    <t>Reverting Override Price to original disables Save on Labor</t>
+  </si>
+  <si>
+    <t>The value 99.99 is entered, then the field is reverted to the original value 13.00.</t>
+  </si>
+  <si>
+    <t>3. Assert saveEnabledAfterEdit=true, saveDisabledAfterRevert=true</t>
+  </si>
+  <si>
+    <t>Editing Override Price to 99.99 enables Save; reverting to the original 13.00 disables Save (no net change). No data is committed - reload would restore regardless</t>
   </si>
   <si>
     <t>TC-CPR-OVR-097</t>
   </si>
   <si>
-    <t>Reverting Override Price to original disables Save on Labor</t>
-  </si>
-  <si>
-    <t>The value 99.99 is entered, then the field is reverted to the original value 13.00.</t>
-  </si>
-  <si>
-    <t>3. Assert saveEnabledAfterEdit=true, saveDisabledAfterRevert=true</t>
-  </si>
-  <si>
-    <t>Editing Override Price to 99.99 enables Save; reverting to the original 13.00 disables Save (no net change). No data is committed - reload would restore regardless</t>
+    <t>Active toggle-then-revert disables Save on Labor</t>
+  </si>
+  <si>
+    <t>The Labor row for PG 565 is displayed with its original Active state.</t>
+  </si>
+  <si>
+    <t>2. Read initial Active state</t>
+  </si>
+  <si>
+    <t>The Active checkbox state is displayed.</t>
+  </si>
+  <si>
+    <t>3. Toggle the Active checkbox</t>
+  </si>
+  <si>
+    <t>The Active checkbox flips to the opposite state and the Save button becomes enabled.</t>
+  </si>
+  <si>
+    <t>4. Toggle the Active checkbox again (revert to original state)</t>
+  </si>
+  <si>
+    <t>Toggling Active then toggling back to the original state leaves zero net change - Save returns to disabled. No data is committed</t>
   </si>
   <si>
     <t>TC-CPR-OVR-098</t>
   </si>
   <si>
-    <t>Active toggle-then-revert disables Save on Labor</t>
-  </si>
-  <si>
-    <t>The Labor row for PG 565 is displayed with its original Active state.</t>
-  </si>
-  <si>
-    <t>2. Read initial Active state</t>
-  </si>
-  <si>
-    <t>The Active checkbox state is displayed.</t>
-  </si>
-  <si>
-    <t>3. Toggle the Active checkbox</t>
-  </si>
-  <si>
-    <t>The Active checkbox flips to the opposite state and the Save button becomes enabled.</t>
-  </si>
-  <si>
-    <t>4. Toggle the Active checkbox again (revert to original state)</t>
-  </si>
-  <si>
-    <t>Toggling Active then toggling back to the original state leaves zero net change - Save returns to disabled. No data is committed</t>
+    <t>Committed - Max Discount % accepts 0 as min valid (Labor)</t>
+  </si>
+  <si>
+    <t>Authenticated, office 1134 selected, Labor tab active, PG 565 row visible</t>
+  </si>
+  <si>
+    <t>1. Navigate to Labor tab on office 1134</t>
+  </si>
+  <si>
+    <t>Office 1134 loads on the Labor tab.</t>
+  </si>
+  <si>
+    <t>2. Find row by product group anchor PG 565</t>
+  </si>
+  <si>
+    <t>The row for Product Group 565 is displayed.</t>
+  </si>
+  <si>
+    <t>3. Call</t>
+  </si>
+  <si>
+    <t>The value 0 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert value commits as 0.00 %</t>
+  </si>
+  <si>
+    <t>The value commits and displays as 0.00 %. Save becomes enabled.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-099</t>
   </si>
   <si>
-    <t>Committed - Max Discount % accepts 0 as min valid (Labor)</t>
-  </si>
-  <si>
-    <t>Authenticated, office 1134 selected, Labor tab active, PG 565 row visible</t>
-  </si>
-  <si>
-    <t>1. Navigate to Labor tab on office 1134</t>
-  </si>
-  <si>
-    <t>Office 1134 loads on the Labor tab.</t>
-  </si>
-  <si>
-    <t>2. Find row by product group anchor PG 565</t>
-  </si>
-  <si>
-    <t>The row for Product Group 565 is displayed.</t>
-  </si>
-  <si>
-    <t>3. Call</t>
-  </si>
-  <si>
-    <t>The value 0 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert value commits as 0.00 %</t>
-  </si>
-  <si>
-    <t>The value commits and displays as 0.00 %. Save becomes enabled.</t>
+    <t>Committed - Max Discount % accepts 50 as mid-value (Labor)</t>
+  </si>
+  <si>
+    <t>Authenticated, office 1134 selected, Labor tab active, PG 893 row visible</t>
+  </si>
+  <si>
+    <t>2. Find row by product group anchor PG 893</t>
+  </si>
+  <si>
+    <t>The row for Product Group 893 is displayed.</t>
+  </si>
+  <si>
+    <t>The value 50 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert value commits as 50.00 %</t>
+  </si>
+  <si>
+    <t>The value commits and displays as 50.00 %. Save becomes enabled.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-100</t>
   </si>
   <si>
-    <t>Committed - Max Discount % accepts 50 as mid-value (Labor)</t>
-  </si>
-  <si>
-    <t>Authenticated, office 1134 selected, Labor tab active, PG 893 row visible</t>
-  </si>
-  <si>
-    <t>2. Find row by product group anchor PG 893</t>
-  </si>
-  <si>
-    <t>The row for Product Group 893 is displayed.</t>
-  </si>
-  <si>
-    <t>The value 50 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert value commits as 50.00 %</t>
-  </si>
-  <si>
-    <t>The value commits and displays as 50.00 %. Save becomes enabled.</t>
+    <t>Committed - Max Discount % accepts 100 as inclusive cap (Labor)</t>
+  </si>
+  <si>
+    <t>The value 100 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert value commits as 100.00 %</t>
+  </si>
+  <si>
+    <t>The value commits and displays as 100.00 %. Save becomes enabled.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-101</t>
   </si>
   <si>
-    <t>Committed - Max Discount % accepts 100 as inclusive cap (Labor)</t>
-  </si>
-  <si>
-    <t>The value 100 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert value commits as 100.00 %</t>
-  </si>
-  <si>
-    <t>The value commits and displays as 100.00 %. Save becomes enabled.</t>
+    <t>Rejected - Max Discount % rejects -0.01 just below minimum (Labor)</t>
+  </si>
+  <si>
+    <t>The value -0.01 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert result matches override rejection signature</t>
+  </si>
+  <si>
+    <t>The value is rejected with an invalid-state indicator. Save remains disabled and the field is escapable.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-102</t>
-  </si>
-  <si>
-    <t>Rejected - Max Discount % rejects -0.01 just below minimum (Labor)</t>
-  </si>
-  <si>
-    <t>The value -0.01 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert result matches override rejection signature</t>
-  </si>
-  <si>
-    <t>The value is rejected with an invalid-state indicator. Save remains disabled and the field is escapable.</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-103</t>
   </si>
   <si>
     <t>Defect - Max Discount % 0.5 misread as 50.00 % (100x multiplier bug, Labor)</t>
@@ -1083,141 +1083,141 @@
     <t>The defect baseline is recorded: 50.00 % is the value displayed for input 0.5 on the Labor tab's Max Discount % field.</t>
   </si>
   <si>
+    <t>TC-CPR-OVR-103</t>
+  </si>
+  <si>
+    <t>Committed - Max Discount % accepts 99.99 just below cap (Labor)</t>
+  </si>
+  <si>
+    <t>The value 99.99 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert value commits as 99.99 %</t>
+  </si>
+  <si>
+    <t>The value commits and displays as 99.99 %. Save becomes enabled.</t>
+  </si>
+  <si>
     <t>TC-CPR-OVR-104</t>
   </si>
   <si>
-    <t>Committed - Max Discount % accepts 99.99 just below cap (Labor)</t>
-  </si>
-  <si>
-    <t>The value 99.99 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert value commits as 99.99 %</t>
-  </si>
-  <si>
-    <t>The value commits and displays as 99.99 %. Save becomes enabled.</t>
+    <t>Rejected - Max Discount % rejects 150 above 100 cap (Labor)</t>
+  </si>
+  <si>
+    <t>The value 150 is entered into the Max Discount % field and Enter is pressed.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-105</t>
   </si>
   <si>
-    <t>Rejected - Max Discount % rejects 150 above 100 cap (Labor)</t>
-  </si>
-  <si>
-    <t>The value 150 is entered into the Max Discount % field and Enter is pressed.</t>
+    <t>Rejected - Max Discount % rejects -5 negative value (Labor)</t>
+  </si>
+  <si>
+    <t>The value -5 is entered into the Max Discount % field and Enter is pressed.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-106</t>
   </si>
   <si>
-    <t>Rejected - Max Discount % rejects -5 negative value (Labor)</t>
-  </si>
-  <si>
-    <t>The value -5 is entered into the Max Discount % field and Enter is pressed.</t>
+    <t>Defect - Max Discount % 'abc' blanks cell to dash, Save stays enabled (Labor)</t>
+  </si>
+  <si>
+    <t>The characters abc are entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert the DEFECT: value blanks to - and Save remains enabled</t>
+  </si>
+  <si>
+    <t>The cell blanks to an em-dash and the Save button remains enabled.</t>
+  </si>
+  <si>
+    <t>The defect is documented for the Labor tab's Max Discount % field.</t>
+  </si>
+  <si>
+    <t>6. - committed = true (editor closes - the app accepted this non-numeric input)</t>
+  </si>
+  <si>
+    <t>The editor closes, confirming the app accepted the non-numeric input.</t>
+  </si>
+  <si>
+    <t>7. - displayedValue = '-' (cell blanked - an emptied discount cap can be saved)</t>
+  </si>
+  <si>
+    <t>The cell displays an em-dash.</t>
+  </si>
+  <si>
+    <t>8. - saveEnabled = true (WRONG - a blanked value should not be saveable)</t>
+  </si>
+  <si>
+    <t>The Save button stays enabled.</t>
+  </si>
+  <si>
+    <t>9. "When the app is fixed": either the input is rejected (editor stays open, committed=false) or Save is disabled. The test fails, exposing the fix</t>
+  </si>
+  <si>
+    <t>The defect baseline is recorded: the Max Discount % cell blanks to an em-dash on the Labor tab with Save left enabled.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-107</t>
   </si>
   <si>
-    <t>Defect - Max Discount % 'abc' blanks cell to dash, Save stays enabled (Labor)</t>
-  </si>
-  <si>
-    <t>The characters abc are entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert the DEFECT: value blanks to - and Save remains enabled</t>
-  </si>
-  <si>
-    <t>The cell blanks to an em-dash and the Save button remains enabled.</t>
-  </si>
-  <si>
-    <t>The defect is documented for the Labor tab's Max Discount % field.</t>
-  </si>
-  <si>
-    <t>6. - committed = true (editor closes - the app accepted this non-numeric input)</t>
-  </si>
-  <si>
-    <t>The editor closes, confirming the app accepted the non-numeric input.</t>
-  </si>
-  <si>
-    <t>7. - displayedValue = '-' (cell blanked - an emptied discount cap can be saved)</t>
-  </si>
-  <si>
-    <t>The cell displays an em-dash.</t>
-  </si>
-  <si>
-    <t>8. - saveEnabled = true (WRONG - a blanked value should not be saveable)</t>
-  </si>
-  <si>
-    <t>The Save button stays enabled.</t>
-  </si>
-  <si>
-    <t>9. "When the app is fixed": either the input is rejected (editor stays open, committed=false) or Save is disabled. The test fails, exposing the fix</t>
-  </si>
-  <si>
-    <t>The defect baseline is recorded: the Max Discount % cell blanks to an em-dash on the Labor tab with Save left enabled.</t>
+    <t>Defect - Max Discount % '1.2.3' silently corrupts to 1.23 % (Labor)</t>
+  </si>
+  <si>
+    <t>The characters 1.2.3 are typed into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert the DEFECT: value commits as 1.23 % (second dot swallowed)</t>
+  </si>
+  <si>
+    <t>The value commits as 1.23 % with the second dot dropped.</t>
+  </si>
+  <si>
+    <t>6. - committed = true (editor closes - should have been rejected)</t>
+  </si>
+  <si>
+    <t>The editor closes, confirming the app accepted the malformed entry.</t>
+  </si>
+  <si>
+    <t>7. - displayedValue = '1.23 %' (WRONG - a multi-dot input is silently corrupted)</t>
+  </si>
+  <si>
+    <t>The cell displays 1.23 % instead of being rejected.</t>
+  </si>
+  <si>
+    <t>9. "When the app is fixed": the input is rejected (editor stays open, committed=false, is invalid). The test fails, naming the change</t>
+  </si>
+  <si>
+    <t>The defect baseline is recorded: 1.2.3 commits as 1.23 % on the Labor tab's Max Discount % field.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-108</t>
   </si>
   <si>
-    <t>Defect - Max Discount % '1.2.3' silently corrupts to 1.23 % (Labor)</t>
-  </si>
-  <si>
-    <t>The characters 1.2.3 are typed into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert the DEFECT: value commits as 1.23 % (second dot swallowed)</t>
-  </si>
-  <si>
-    <t>The value commits as 1.23 % with the second dot dropped.</t>
-  </si>
-  <si>
-    <t>6. - committed = true (editor closes - should have been rejected)</t>
-  </si>
-  <si>
-    <t>The editor closes, confirming the app accepted the malformed entry.</t>
-  </si>
-  <si>
-    <t>7. - displayedValue = '1.23 %' (WRONG - a multi-dot input is silently corrupted)</t>
-  </si>
-  <si>
-    <t>The cell displays 1.23 % instead of being rejected.</t>
-  </si>
-  <si>
-    <t>9. "When the app is fixed": the input is rejected (editor stays open, committed=false, is invalid). The test fails, naming the change</t>
-  </si>
-  <si>
-    <t>The defect baseline is recorded: 1.2.3 commits as 1.23 % on the Labor tab's Max Discount % field.</t>
+    <t>Committed - Max Discount % strips leading zeros from 007 (Labor)</t>
+  </si>
+  <si>
+    <t>The value 007 is entered into the Max Discount % field and Enter is pressed.</t>
+  </si>
+  <si>
+    <t>4. Assert value commits with leading zeros stripped</t>
+  </si>
+  <si>
+    <t>The value commits with leading zeros stripped and displays as 7.00 %. Save becomes enabled.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-109</t>
   </si>
   <si>
-    <t>Committed - Max Discount % strips leading zeros from 007 (Labor)</t>
-  </si>
-  <si>
-    <t>The value 007 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>4. Assert value commits with leading zeros stripped</t>
-  </si>
-  <si>
-    <t>The value commits with leading zeros stripped and displays as 7.00 %. Save becomes enabled.</t>
+    <t>Rejected - Max Discount % rejects scientific notation 1e5 (Labor)</t>
+  </si>
+  <si>
+    <t>The value 1e5 is entered into the Max Discount % field and Enter is pressed.</t>
   </si>
   <si>
     <t>TC-CPR-OVR-110</t>
   </si>
   <si>
-    <t>Rejected - Max Discount % rejects scientific notation 1e5 (Labor)</t>
-  </si>
-  <si>
-    <t>The value 1e5 is entered into the Max Discount % field and Enter is pressed.</t>
-  </si>
-  <si>
-    <t>TC-CPR-OVR-111</t>
-  </si>
-  <si>
     <t>Save-cycle - reverting Max Discount % to original disables Save on Labor</t>
   </si>
   <si>
@@ -1230,7 +1230,7 @@
     <t>Save enables after editing to a new value and disables after reverting to the original value.</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-119</t>
+    <t>TC-CPR-OVR-118</t>
   </si>
   <si>
     <t>Sort produces verifiable monotonic order on Labor tab</t>
@@ -1288,7 +1288,7 @@
     <t>The Product Group values are displayed in non-decreasing order.</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-121</t>
+    <t>TC-CPR-OVR-120</t>
   </si>
   <si>
     <t>Select 10 rows-per-page -&gt; grid renders exactly 10 rows (OVR-RPP-2)</t>
@@ -1333,7 +1333,7 @@
     <t>Selecting "10" re-renders the grid to show exactly 10 rows on page 1. The pagination updates to reflect 10-row pages. The default of 20 differs from 10, so this assertion "fails if the control does nothing" (an inactive control yields 20 visible rows ≠ 10)</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-122</t>
+    <t>TC-CPR-OVR-121</t>
   </si>
   <si>
     <t>Select 30 rows-per-page -&gt; grid renders exactly 30 rows (OVR-RPP-4)</t>
@@ -1360,7 +1360,7 @@
     <t>Selecting "30" re-renders the grid to show exactly 30 rows on page 1. The pagination updates to reflect 30-row pages. The default of 20 differs from 30, so this assertion "fails if the control does nothing" (an inactive control yields 20 visible rows ≠ 30)</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-123</t>
+    <t>TC-CPR-OVR-122</t>
   </si>
   <si>
     <t>Select 40 rows-per-page -&gt; grid renders exactly 40 rows (OVR-RPP-5)</t>
@@ -1384,7 +1384,7 @@
     <t>Selecting "40" re-renders the grid to show exactly 40 rows on page 1. The pagination updates to reflect 40-row pages. The default of 20 differs from 40, so this assertion "fails if the control does nothing" (an inactive control yields 20 visible rows ≠ 40)</t>
   </si>
   <si>
-    <t>TC-CPR-OVR-124</t>
+    <t>TC-CPR-OVR-123</t>
   </si>
   <si>
     <t>Select 50 rows-per-page -&gt; grid renders exactly 50 rows (OVR-RPP-6)</t>
@@ -1420,7 +1420,7 @@
     <t>Pass:48 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-07-27</t>
+    <t>Last Updated: 2026-07-30</t>
   </si>
 </sst>
 </file>
